--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486523_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486523_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.37</v>
+        <v>4.4686</v>
       </c>
       <c r="E2" t="n">
-        <v>5.589</v>
+        <v>1.2707</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.219</v>
+        <v>3.1979</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8711</v>
+        <v>2.5852</v>
       </c>
       <c r="H2" t="n">
-        <v>3.656</v>
+        <v>0.7206</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7849</v>
+        <v>1.8646</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6744</v>
+        <v>1.1733</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6744</v>
+        <v>-0.4531</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.6264</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8033</v>
+        <v>1.4119</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0184</v>
+        <v>1.1737</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7849</v>
+        <v>0.2382</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>1.9576</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3037</v>
+        <v>-0.0742</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5692</v>
+        <v>0.0973</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2656</v>
+        <v>-0.1716</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.908</v>
+        <v>3.7621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9779</v>
+        <v>3.9812</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9301</v>
+        <v>-0.219</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7706</v>
+        <v>2.8711</v>
       </c>
       <c r="H3" t="n">
-        <v>2.275</v>
+        <v>3.656</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4956</v>
+        <v>-0.7849</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4519</v>
+        <v>3.6744</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2989</v>
+        <v>3.6744</v>
       </c>
       <c r="L3" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3187</v>
+        <v>-0.8033</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9761</v>
+        <v>-0.0184</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3426</v>
+        <v>-0.7849</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2244</v>
+        <v>0.6958</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2656</v>
+        <v>0.9614</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9588</v>
+        <v>-0.2656</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7395</v>
+        <v>1.5204</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4568</v>
+        <v>3.3707</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3514</v>
+        <v>0.7796</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1054</v>
+        <v>2.591</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5852</v>
+        <v>2.7706</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7206</v>
+        <v>2.275</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8646</v>
+        <v>0.4956</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1733</v>
+        <v>1.4519</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4531</v>
+        <v>1.2989</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6264</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4119</v>
+        <v>1.3187</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1737</v>
+        <v>0.9761</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2382</v>
+        <v>0.3426</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.086</v>
+        <v>0.6871</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.822</v>
+        <v>0.0673</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.264</v>
+        <v>0.6198</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3872</v>
+        <v>2.9588</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4206</v>
+        <v>-0.8799</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8078</v>
+        <v>3.8386</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7285</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4435</v>
+        <v>1.0151</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1454</v>
+        <v>0.3954</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5889</v>
+        <v>0.6198</v>
       </c>
       <c r="V5" t="n">
         <v>3.7597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9916</v>
+        <v>1.9222</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4197</v>
+        <v>2.1962</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4281</v>
+        <v>-0.274</v>
       </c>
       <c r="G6" t="n">
         <v>2.5821</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1268</v>
+        <v>0.0574</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4711</v>
+        <v>0.2476</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9347</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9052</v>
+        <v>0.3072</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1896</v>
+        <v>-1.2328</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0948</v>
+        <v>1.54</v>
       </c>
       <c r="G7" t="n">
         <v>1.0511</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.964</v>
+        <v>0.3659</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0517</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9724</v>
+        <v>0.4176</v>
       </c>
       <c r="V7" t="n">
         <v>0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5149</v>
+        <v>-0.4841</v>
       </c>
       <c r="E8" t="n">
         <v>-0.137</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3779</v>
+        <v>-0.3471</v>
       </c>
       <c r="G8" t="n">
         <v>-0.616</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1164</v>
+        <v>-0.0856</v>
       </c>
       <c r="T8" t="n">
         <v>-0.137</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3646</v>
+        <v>-1.0619</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2716</v>
+        <v>-0.2464</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.093</v>
+        <v>-0.8156</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1342</v>
@@ -1156,13 +1156,13 @@
         <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1455</v>
+        <v>0.1571</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1971</v>
+        <v>0.2223</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3426</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.642</v>
+        <v>-1.1526</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6648</v>
+        <v>-1.3296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0229</v>
+        <v>0.177</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1233</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3887</v>
+        <v>0.1006</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6764</v>
+        <v>-1.2361</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1203</v>
+        <v>-2.3274</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4439</v>
+        <v>1.0913</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2265</v>
+        <v>2.6825</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6935</v>
+        <v>5.803</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.467</v>
+        <v>-3.1205</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4467</v>
+        <v>2.8451</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0434</v>
+        <v>4.9273</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4901</v>
+        <v>-2.0822</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6732</v>
+        <v>-0.1627</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3499</v>
+        <v>0.8757</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0231</v>
+        <v>-1.0383</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3926</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3803</v>
+        <v>0.256</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.0829</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0306</v>
+        <v>0.3389</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.4345</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0436</v>
+        <v>-1.315</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.135</v>
+        <v>-1.6048</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0913</v>
+        <v>0.2898</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6825</v>
+        <v>0.2265</v>
       </c>
       <c r="H12" t="n">
-        <v>5.803</v>
+        <v>0.6935</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1205</v>
+        <v>-0.467</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8451</v>
+        <v>-0.4467</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9273</v>
+        <v>1.0434</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0822</v>
+        <v>-1.4901</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1627</v>
+        <v>0.6732</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8757</v>
+        <v>-0.3499</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0383</v>
+        <v>1.0231</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7401</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.3501</v>
+        <v>-2.3926</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6101</v>
+        <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5516</v>
+        <v>-0.0189</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>0.1046</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3389</v>
+        <v>-0.1235</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4345</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.436</v>
+        <v>-6.171</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8392</v>
+        <v>-5.8825</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5967</v>
+        <v>-0.2885</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3294</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8015</v>
+        <v>-0.5366</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1971</v>
+        <v>0.1538</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9986</v>
+        <v>-0.6904</v>
       </c>
       <c r="V13" t="n">
         <v>-1.695</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3413</v>
+        <v>5.368900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.440099999999999</v>
+        <v>-5.4127</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7815</v>
+        <v>10.7814</v>
       </c>
       <c r="G14" t="n">
-        <v>8.837699999999998</v>
+        <v>8.8377</v>
       </c>
       <c r="H14" t="n">
         <v>13.1848</v>
@@ -1546,13 +1546,13 @@
         <v>17.4006</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5924</v>
+        <v>2.6197</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9433999999999998</v>
+        <v>1.9709</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6486999999999999</v>
+        <v>0.6488000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>-3.9135</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1171</v>
+        <v>2.988</v>
       </c>
       <c r="E15" t="n">
-        <v>1.787</v>
+        <v>0.7811</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3301</v>
+        <v>2.2068</v>
       </c>
       <c r="G15" t="n">
         <v>0.5862000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>3.0451</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4884</v>
+        <v>0.3593</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2318</v>
+        <v>0.2259</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2567</v>
+        <v>0.1334</v>
       </c>
       <c r="V15" t="n">
         <v>2.2599</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9298</v>
+        <v>2.5714</v>
       </c>
       <c r="E16" t="n">
-        <v>2.597</v>
+        <v>2.4853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3327</v>
+        <v>0.0862</v>
       </c>
       <c r="G16" t="n">
         <v>2.0881</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4881</v>
+        <v>0.1298</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0721</v>
+        <v>-0.0396</v>
       </c>
       <c r="U16" t="n">
-        <v>0.416</v>
+        <v>0.1694</v>
       </c>
       <c r="V16" t="n">
         <v>-1.169</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2774</v>
+        <v>0.9306</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3731</v>
+        <v>1.1496</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.219</v>
       </c>
       <c r="G17" t="n">
         <v>0.09909999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1353</v>
+        <v>-0.2115</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2091</v>
+        <v>-0.0144</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0738</v>
+        <v>-0.1971</v>
       </c>
       <c r="V17" t="n">
         <v>0.3904</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1516</v>
+        <v>0.6818</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5175</v>
+        <v>-1.5115</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3659</v>
+        <v>2.1933</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1862</v>
+        <v>-1.09</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3049</v>
+        <v>0.4926</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1187</v>
+        <v>-1.5826</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7669</v>
+        <v>-1.2827</v>
       </c>
       <c r="K18" t="n">
-        <v>0.073</v>
+        <v>0.876</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8399</v>
+        <v>-2.1587</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4193</v>
+        <v>0.1927</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3779</v>
+        <v>-0.3834</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9586</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5552</v>
+        <v>-0.2539</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4817</v>
+        <v>-0.3136</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0735</v>
+        <v>0.0598</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.0257</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8902</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0094</v>
+        <v>0.2074</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3997</v>
+        <v>0.5117</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4091</v>
+        <v>-0.3043</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.09</v>
+        <v>-1.1862</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4926</v>
+        <v>-1.3049</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5826</v>
+        <v>0.1187</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2827</v>
+        <v>-0.7669</v>
       </c>
       <c r="K19" t="n">
-        <v>0.876</v>
+        <v>0.073</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1587</v>
+        <v>-0.8399</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1927</v>
+        <v>-0.4193</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3834</v>
+        <v>-1.3779</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.9586</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0737</v>
+        <v>0.6111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2019</v>
+        <v>0.4759</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2755</v>
+        <v>0.1352</v>
       </c>
       <c r="V19" t="n">
-        <v>2.0257</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>1.8902</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2343</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.606</v>
+        <v>-0.2942</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1672</v>
+        <v>-0.7088</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4388</v>
+        <v>0.4146</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4622</v>
+        <v>-0.0487</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1825</v>
+        <v>-0.0487</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2797</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0382</v>
+        <v>-0.7268</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>-0.7451</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5004</v>
+        <v>0.6781</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1825</v>
+        <v>-0.067</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.318</v>
+        <v>0.7451</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,28 +2014,28 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1438</v>
+        <v>-0.2064</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0616</v>
+        <v>-0.2244</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6101</v>
+        <v>-0.3284</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9323</v>
+        <v>-0.7602</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3222</v>
+        <v>0.4318</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0487</v>
+        <v>0.4791</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0487</v>
+        <v>-1.29</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.7691</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7268</v>
+        <v>1.7982</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0182</v>
+        <v>0.4562</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7451</v>
+        <v>1.342</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6781</v>
+        <v>-1.3191</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.067</v>
+        <v>-1.7462</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7451</v>
+        <v>0.4271</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.9151</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5224</v>
+        <v>-0.9881</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2055</v>
+        <v>-0.3833</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3169</v>
+        <v>-0.6048</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.039</v>
+        <v>-1.5595</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.039</v>
+        <v>-1.5595</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3766</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6543</v>
+        <v>-0.1672</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2777</v>
+        <v>-0.3463</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4791</v>
+        <v>-0.4622</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.29</v>
+        <v>-0.1825</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7691</v>
+        <v>-0.2797</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7982</v>
+        <v>0.0382</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4562</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.342</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3191</v>
+        <v>-0.5004</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7462</v>
+        <v>-0.1825</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4271</v>
+        <v>-0.318</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.9151</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0363</v>
+        <v>-0.0514</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2774</v>
+        <v>-0.2055</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7589</v>
+        <v>0.1541</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5595</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.359</v>
+        <v>-3.28</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6965</v>
+        <v>-3.8024</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3374</v>
+        <v>0.5224</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8231</v>
@@ -2248,13 +2248,13 @@
         <v>3.2626</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8667</v>
+        <v>-0.7877</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2089</v>
+        <v>-0.3148</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.4729</v>
       </c>
       <c r="V23" t="n">
         <v>0.3307</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.8748</v>
+        <v>-7.3045</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.206200000000001</v>
+        <v>-8.7591</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3314</v>
+        <v>1.4547</v>
       </c>
       <c r="G24" t="n">
         <v>-6.4802</v>
@@ -2326,13 +2326,13 @@
         <v>2.6101</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7638</v>
+        <v>-0.1935</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5444</v>
+        <v>-0.0973</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2194</v>
+        <v>-0.0961</v>
       </c>
       <c r="V24" t="n">
         <v>1.1093</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3412</v>
+        <v>-4.3415</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.7816</v>
+        <v>-10.7815</v>
       </c>
       <c r="F25" t="n">
-        <v>6.440199999999999</v>
+        <v>6.4402</v>
       </c>
       <c r="G25" t="n">
         <v>-8.837900000000001</v>
@@ -2383,7 +2383,7 @@
         <v>-2.6289</v>
       </c>
       <c r="L25" t="n">
-        <v>0.07580000000000009</v>
+        <v>0.07579999999999987</v>
       </c>
       <c r="M25" t="n">
         <v>-6.284899999999999</v>
@@ -2407,10 +2407,10 @@
         <v>-1.5923</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6489000000000003</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9435000000000002</v>
+        <v>-0.9434</v>
       </c>
       <c r="V25" t="n">
         <v>3.9135</v>
